--- a/artfynd/A 36750-2023 artfynd.xlsx
+++ b/artfynd/A 36750-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36750-2023 artfynd.xlsx
+++ b/artfynd/A 36750-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109475151</v>
+        <v>109475159</v>
       </c>
       <c r="B2" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båthussjön, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504258</v>
+        <v>504139</v>
       </c>
       <c r="R2" t="n">
-        <v>6877975</v>
+        <v>6877867</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109475159</v>
+        <v>109475161</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504138.6761097718</v>
+        <v>504262</v>
       </c>
       <c r="R3" t="n">
-        <v>6877866.945714471</v>
+        <v>6877996</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -914,6 +890,131 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109475151</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Båthussjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504258</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6877975</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 36750-2023 artfynd.xlsx
+++ b/artfynd/A 36750-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109475159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109475161</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,8 +1034,18 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109475151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>